--- a/automation/test_data.xlsx
+++ b/automation/test_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Snehal Ninawe\OneDrive\Desktop\Don Bosco\automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2582D719-3BDD-41C6-934B-5434C01D20DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{900AE562-AA29-4CDE-8C1F-3E2E12FE84B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="14" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Section" sheetId="1" r:id="rId1"/>
@@ -27,13 +27,16 @@
     <sheet name="AI TEST CASES-4(TOPIC)" sheetId="12" r:id="rId12"/>
     <sheet name="AI TEST CASES-5(SUBJECT)" sheetId="13" r:id="rId13"/>
     <sheet name="AI TEST CASES-6(Branch)" sheetId="14" r:id="rId14"/>
+    <sheet name="AI TEST CASES-7(TLP)" sheetId="15" r:id="rId15"/>
+    <sheet name="AI TEST CASES-8(Promotion)" sheetId="16" r:id="rId16"/>
+    <sheet name="Student promotion" sheetId="17" r:id="rId17"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3458" uniqueCount="1720">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4046" uniqueCount="1924">
   <si>
     <t>Subject Name</t>
   </si>
@@ -5193,13 +5196,625 @@
   </si>
   <si>
     <t>Different Prefix</t>
+  </si>
+  <si>
+    <t>TLP-001</t>
+  </si>
+  <si>
+    <t>Unit Plan - Teaching Learning Plan</t>
+  </si>
+  <si>
+    <t>Open Teaching Learning Plan page</t>
+  </si>
+  <si>
+    <t>Open Unit Plan; select Teaching Learning Plan.</t>
+  </si>
+  <si>
+    <t>TLP listing opens and displays available row actions.</t>
+  </si>
+  <si>
+    <t>TLP-002</t>
+  </si>
+  <si>
+    <t>Open selected TLP detail view</t>
+  </si>
+  <si>
+    <t>A TLP row exists in the listing.</t>
+  </si>
+  <si>
+    <t>Open the row’s action menu; select View.</t>
+  </si>
+  <si>
+    <t>Target TLP record</t>
+  </si>
+  <si>
+    <t>The selected TLP’s details are displayed.</t>
+  </si>
+  <si>
+    <t>TLP-003</t>
+  </si>
+  <si>
+    <t>Open Approve action modal</t>
+  </si>
+  <si>
+    <t>TLP detail view is open and Approve is available.</t>
+  </si>
+  <si>
+    <t>Select Approve.</t>
+  </si>
+  <si>
+    <t>Approval modal opens with a comment field and submit control.</t>
+  </si>
+  <si>
+    <t>TLP-004</t>
+  </si>
+  <si>
+    <t>Submit approval with valid comment</t>
+  </si>
+  <si>
+    <t>Approval modal is open.</t>
+  </si>
+  <si>
+    <t>Enter a comment; click Submit.</t>
+  </si>
+  <si>
+    <t>Comment=Approved</t>
+  </si>
+  <si>
+    <t>Approval completes; a success message appears or the modal closes.</t>
+  </si>
+  <si>
+    <t>TLP-005</t>
+  </si>
+  <si>
+    <t>Submit approval with empty comment</t>
+  </si>
+  <si>
+    <t>Leave the comment blank; click Submit.</t>
+  </si>
+  <si>
+    <t>Comment=Blank</t>
+  </si>
+  <si>
+    <t>If a comment is required, validation appears and approval is blocked. If optional, approval proceeds. Record the actual behavior.</t>
+  </si>
+  <si>
+    <t>TLP-006</t>
+  </si>
+  <si>
+    <t>Submit approval with whitespace-only comment</t>
+  </si>
+  <si>
+    <t>Enter three spaces in the comment field; click Submit.</t>
+  </si>
+  <si>
+    <t>Comment=</t>
+  </si>
+  <si>
+    <t>System applies its actual validation or trimming behavior; no assumption is made that whitespace is valid or invalid.</t>
+  </si>
+  <si>
+    <t>TLP-007</t>
+  </si>
+  <si>
+    <t>Special characters are retained in comment field</t>
+  </si>
+  <si>
+    <t>Enter the special-character comment; inspect the field before submitting.</t>
+  </si>
+  <si>
+    <t>Comment=@#$%^&amp;*()_+-=Test</t>
+  </si>
+  <si>
+    <t>Comment retains the entered characters without corruption.</t>
+  </si>
+  <si>
+    <t>TLP-008</t>
+  </si>
+  <si>
+    <t>Long comment is handled</t>
+  </si>
+  <si>
+    <t>Enter a 500-character comment; inspect the field and any validation.</t>
+  </si>
+  <si>
+    <t>Comment=500 A characters</t>
+  </si>
+  <si>
+    <t>Text is not silently corrupted; any application length restriction is clearly enforced.</t>
+  </si>
+  <si>
+    <t>TLP-009</t>
+  </si>
+  <si>
+    <t>Restore valid comment after input checks</t>
+  </si>
+  <si>
+    <t>Approval modal remains open after comment checks.</t>
+  </si>
+  <si>
+    <t>Replace the current comment with the valid comment; inspect the field.</t>
+  </si>
+  <si>
+    <t>The field displays exactly Approved before final submission.</t>
+  </si>
+  <si>
+    <t>TLP-010</t>
+  </si>
+  <si>
+    <t>Verify approval completion result</t>
+  </si>
+  <si>
+    <t>Approval modal contains the valid comment.</t>
+  </si>
+  <si>
+    <t>Click Submit; observe the result.</t>
+  </si>
+  <si>
+    <t>A visible success message appears or the approval modal closes.</t>
+  </si>
+  <si>
+    <t>TLP-011</t>
+  </si>
+  <si>
+    <t>Verify approval submit control is usable</t>
+  </si>
+  <si>
+    <t>Inspect and click the submit control.</t>
+  </si>
+  <si>
+    <t>Submit control</t>
+  </si>
+  <si>
+    <t>Submit control is available and clickable.</t>
+  </si>
+  <si>
+    <t>TLP-012</t>
+  </si>
+  <si>
+    <t>Correct invalid comment after validation</t>
+  </si>
+  <si>
+    <t>A comment validation condition is triggered.</t>
+  </si>
+  <si>
+    <t>Observe validation; replace the comment with Approved; submit again.</t>
+  </si>
+  <si>
+    <t>Initial comment=Blank or spaces; corrected comment=Approved</t>
+  </si>
+  <si>
+    <t>User can correct the comment and submit the approval successfully.</t>
+  </si>
+  <si>
+    <t>TLP-013</t>
+  </si>
+  <si>
+    <t>Approval action applies to the selected TLP</t>
+  </si>
+  <si>
+    <t>Multiple TLP records exist and the target record is identified.</t>
+  </si>
+  <si>
+    <t>Open View and Approve from the target TLP row; submit approval.</t>
+  </si>
+  <si>
+    <t>Identified target TLP</t>
+  </si>
+  <si>
+    <t>Approval action is applied to the selected record, not another TLP row.</t>
+  </si>
+  <si>
+    <t>TLP-014</t>
+  </si>
+  <si>
+    <t>Comment entry alone does not submit approval</t>
+  </si>
+  <si>
+    <t>Enter or change the comment; do not click Submit.</t>
+  </si>
+  <si>
+    <t>Approval is not submitted until the Submit control is clicked.</t>
+  </si>
+  <si>
+    <t>PROM-001</t>
+  </si>
+  <si>
+    <t>Student Promotion</t>
+  </si>
+  <si>
+    <t>Open Student Promotion from Student Info</t>
+  </si>
+  <si>
+    <t>User is authenticated and has access to Student Info.</t>
+  </si>
+  <si>
+    <t>Open Student Info; select Student Promotion.</t>
+  </si>
+  <si>
+    <t>Student Promotion page opens with the academic filters displayed.</t>
+  </si>
+  <si>
+    <t>PROM-002</t>
+  </si>
+  <si>
+    <t>Select valid academic filters</t>
+  </si>
+  <si>
+    <t>Academic hierarchy values exist.</t>
+  </si>
+  <si>
+    <t>Select Branch, Department, Program and Semester.</t>
+  </si>
+  <si>
+    <t>Branch=RTM,Marol(West),Mumbai-400021; Department=CSE-2026; Program=new-btech; Semester=Sem-3(CSE)</t>
+  </si>
+  <si>
+    <t>PROM-003</t>
+  </si>
+  <si>
+    <t>Verify dependent academic dropdowns</t>
+  </si>
+  <si>
+    <t>Dependent hierarchy values are configured.</t>
+  </si>
+  <si>
+    <t>Select Branch, Department and Program; inspect the following dropdowns.</t>
+  </si>
+  <si>
+    <t>Branch=RTM,Marol(West),Mumbai-400021; Department=CSE-2026; Program=new-btech</t>
+  </si>
+  <si>
+    <t>Dependent dropdowns show values relevant to previous selections where configured.</t>
+  </si>
+  <si>
+    <t>PROM-004</t>
+  </si>
+  <si>
+    <t>Search students with valid filters</t>
+  </si>
+  <si>
+    <t>All academic filters are selected.</t>
+  </si>
+  <si>
+    <t>Click Search.</t>
+  </si>
+  <si>
+    <t>Valid Branch, Department, Program and Semester</t>
+  </si>
+  <si>
+    <t>Search results contain students matching the selected academic hierarchy.</t>
+  </si>
+  <si>
+    <t>PROM-005</t>
+  </si>
+  <si>
+    <t>Search is blocked or the applicable validation is displayed.</t>
+  </si>
+  <si>
+    <t>PROM-006</t>
+  </si>
+  <si>
+    <t>Branch, Program and Semester are selected.</t>
+  </si>
+  <si>
+    <t>PROM-007</t>
+  </si>
+  <si>
+    <t>Branch, Department and Semester are selected.</t>
+  </si>
+  <si>
+    <t>PROM-008</t>
+  </si>
+  <si>
+    <t>Branch, Department and Program are selected.</t>
+  </si>
+  <si>
+    <t>PROM-009</t>
+  </si>
+  <si>
+    <t>Search returns no matching students</t>
+  </si>
+  <si>
+    <t>A valid hierarchy with no matching students is available.</t>
+  </si>
+  <si>
+    <t>Select the hierarchy; click Search.</t>
+  </si>
+  <si>
+    <t>Hierarchy with no matching students</t>
+  </si>
+  <si>
+    <t>An empty result state is displayed; unrelated students are not listed.</t>
+  </si>
+  <si>
+    <t>PROM-010</t>
+  </si>
+  <si>
+    <t>Select a student checkbox</t>
+  </si>
+  <si>
+    <t>Search results include the target student.</t>
+  </si>
+  <si>
+    <t>Select the target student’s checkbox.</t>
+  </si>
+  <si>
+    <t>Eligible student from search results</t>
+  </si>
+  <si>
+    <t>The checkbox changes to selected.</t>
+  </si>
+  <si>
+    <t>PROM-011</t>
+  </si>
+  <si>
+    <t>Verify selected checkbox state</t>
+  </si>
+  <si>
+    <t>The target student checkbox has been selected.</t>
+  </si>
+  <si>
+    <t>Locate the same student again; verify the checkbox state.</t>
+  </si>
+  <si>
+    <t>Selected student</t>
+  </si>
+  <si>
+    <t>The checkbox remains selected before promotion.</t>
+  </si>
+  <si>
+    <t>PROM-012</t>
+  </si>
+  <si>
+    <t>Deselect a selected student</t>
+  </si>
+  <si>
+    <t>A student checkbox is selected.</t>
+  </si>
+  <si>
+    <t>Click the selected checkbox again.</t>
+  </si>
+  <si>
+    <t>The checkbox becomes unselected.</t>
+  </si>
+  <si>
+    <t>PROM-013</t>
+  </si>
+  <si>
+    <t>Open promotion modal after student selection</t>
+  </si>
+  <si>
+    <t>At least one student is selected.</t>
+  </si>
+  <si>
+    <t>Click the promotion action.</t>
+  </si>
+  <si>
+    <t>A visible promotion modal opens.</t>
+  </si>
+  <si>
+    <t>PROM-014</t>
+  </si>
+  <si>
+    <t>Attempt promotion without selecting a student</t>
+  </si>
+  <si>
+    <t>Search results are displayed and no student is selected.</t>
+  </si>
+  <si>
+    <t>No selected students</t>
+  </si>
+  <si>
+    <t>Promotion is blocked or handled without promoting an unintended student.</t>
+  </si>
+  <si>
+    <t>PROM-015</t>
+  </si>
+  <si>
+    <t>Select valid Target Section</t>
+  </si>
+  <si>
+    <t>Promotion modal is open and the target section is available.</t>
+  </si>
+  <si>
+    <t>Open Target Section; select a section.</t>
+  </si>
+  <si>
+    <t>Target Section=CSE-Section A</t>
+  </si>
+  <si>
+    <t>The selected Target Section is displayed correctly.</t>
+  </si>
+  <si>
+    <t>PROM-016</t>
+  </si>
+  <si>
+    <t>Submit promotion with valid student and section</t>
+  </si>
+  <si>
+    <t>A student is selected and the promotion modal is open.</t>
+  </si>
+  <si>
+    <t>Select Target Section; click Submit Promotion.</t>
+  </si>
+  <si>
+    <t>Student=selected eligible student; Target Section=CSE-Section A</t>
+  </si>
+  <si>
+    <t>Promotion completes and a success message is displayed.</t>
+  </si>
+  <si>
+    <t>PROM-017</t>
+  </si>
+  <si>
+    <t>Submit without selecting Target Section</t>
+  </si>
+  <si>
+    <t>Leave Target Section blank; click Submit Promotion.</t>
+  </si>
+  <si>
+    <t>Target Section=Blank</t>
+  </si>
+  <si>
+    <t>Submission is blocked or the applicable validation is displayed.</t>
+  </si>
+  <si>
+    <t>PROM-018</t>
+  </si>
+  <si>
+    <t>Verify promotion success message</t>
+  </si>
+  <si>
+    <t>Promotion was submitted with a selected student and section.</t>
+  </si>
+  <si>
+    <t>Observe the application response after submission.</t>
+  </si>
+  <si>
+    <t>A visible success message is displayed.</t>
+  </si>
+  <si>
+    <t>PROM-019</t>
+  </si>
+  <si>
+    <t>Verify selected Target Section is used</t>
+  </si>
+  <si>
+    <t>A student and valid Target Section are selected.</t>
+  </si>
+  <si>
+    <t>Submit the promotion; inspect the student’s resulting section or promotion state.</t>
+  </si>
+  <si>
+    <t>The selected student is promoted to the selected Target Section.</t>
+  </si>
+  <si>
+    <t>PROM-020</t>
+  </si>
+  <si>
+    <t>Verify results after promotion</t>
+  </si>
+  <si>
+    <t>Promotion completed successfully.</t>
+  </si>
+  <si>
+    <t>Refresh or search the same academic hierarchy again.</t>
+  </si>
+  <si>
+    <t>Previously promoted student</t>
+  </si>
+  <si>
+    <t>The refreshed results reflect the updated promotion state as shown by the application.</t>
+  </si>
+  <si>
+    <t>PROM-021</t>
+  </si>
+  <si>
+    <t>Verify promotion modal before submission</t>
+  </si>
+  <si>
+    <t>A student is selected.</t>
+  </si>
+  <si>
+    <t>Click the promotion action; inspect the modal before submitting.</t>
+  </si>
+  <si>
+    <t>The modal is visible and allows the target section to be selected before submission.</t>
+  </si>
+  <si>
+    <t>Student Checkbox ID</t>
+  </si>
+  <si>
+    <t>student_record_3357</t>
+  </si>
+  <si>
+    <t>Student Promotion page should open successfully</t>
+  </si>
+  <si>
+    <t>Valid academic filters should be selected successfully</t>
+  </si>
+  <si>
+    <t>Dependent dropdowns should display relevant options</t>
+  </si>
+  <si>
+    <t>Matching students should be displayed after search</t>
+  </si>
+  <si>
+    <t>Branch validation should appear or search should be blocked</t>
+  </si>
+  <si>
+    <t>Department validation should appear or search should be blocked</t>
+  </si>
+  <si>
+    <t>Program validation should appear or search should be blocked</t>
+  </si>
+  <si>
+    <t>Semester validation should appear or search should be blocked</t>
+  </si>
+  <si>
+    <t>No matching students should be displayed for the selected filters</t>
+  </si>
+  <si>
+    <t>Student checkbox should be selectable</t>
+  </si>
+  <si>
+    <t>Selected student checkbox should remain checked</t>
+  </si>
+  <si>
+    <t>Selected student checkbox should become unchecked after deselection</t>
+  </si>
+  <si>
+    <t>Promotion modal should open after selecting a student</t>
+  </si>
+  <si>
+    <t>Promotion should be blocked when no student is selected</t>
+  </si>
+  <si>
+    <t>Target Section should be selectable</t>
+  </si>
+  <si>
+    <t>Student should be promoted successfully to the selected section</t>
+  </si>
+  <si>
+    <t>Promotion should be blocked when Target Section is not selected</t>
+  </si>
+  <si>
+    <t>Success message should appear after promotion</t>
+  </si>
+  <si>
+    <t>Student should be assigned to the selected Target Section</t>
+  </si>
+  <si>
+    <t>Updated student records should be displayed correctly</t>
+  </si>
+  <si>
+    <t>Promotion modal should display the required fields before submission</t>
+  </si>
+  <si>
+    <t>Student should be promoted to the selected alternate section</t>
+  </si>
+  <si>
+    <t>Invalid Section</t>
+  </si>
+  <si>
+    <t>Invalid Target Section should be rejected</t>
+  </si>
+  <si>
+    <t>student_record_9999</t>
+  </si>
+  <si>
+    <t>Invalid student ID should not be selected or promoted</t>
+  </si>
+  <si>
+    <t>Valid promotion should succeed when retry is enabled</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5273,6 +5888,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF383838"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -5310,7 +5931,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5353,6 +5974,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -12358,6 +12982,2072 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0571E0A9-38C9-438D-AB33-810F7EA55E90}">
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="10.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" customWidth="1"/>
+    <col min="6" max="6" width="23.88671875" customWidth="1"/>
+    <col min="7" max="7" width="16.5546875" customWidth="1"/>
+    <col min="8" max="8" width="28.6640625" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="27" thickBot="1">
+      <c r="A1" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="40.200000000000003" thickBot="1">
+      <c r="A2" s="11">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>1720</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>1721</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>1722</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>924</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>1723</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>1724</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="27" thickBot="1">
+      <c r="A3" s="11">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>1725</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>1721</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>1726</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>1727</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>1728</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>1729</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>1730</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="40.200000000000003" thickBot="1">
+      <c r="A4" s="11">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>1731</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>1721</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>1732</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>1733</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>1734</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>1729</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>1735</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="53.4" thickBot="1">
+      <c r="A5" s="11">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>1736</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>1721</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>1737</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>1738</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>1739</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>1740</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>1741</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="79.8" thickBot="1">
+      <c r="A6" s="11">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>1742</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>1721</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>1743</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>1738</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>1744</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>1745</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>1746</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="66.599999999999994" thickBot="1">
+      <c r="A7" s="11">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>1747</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>1721</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>1748</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>1738</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>1749</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>1750</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>1751</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="40.200000000000003" thickBot="1">
+      <c r="A8" s="11">
+        <v>7</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>1752</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>1721</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>1753</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>1738</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>1754</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>1755</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>1756</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="66.599999999999994" thickBot="1">
+      <c r="A9" s="11">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>1757</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>1721</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>1758</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>1738</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>1759</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>1760</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>1761</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="40.200000000000003" thickBot="1">
+      <c r="A10" s="11">
+        <v>9</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>1762</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>1721</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>1763</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>1764</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>1765</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>1740</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>1766</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="40.200000000000003" thickBot="1">
+      <c r="A11" s="11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>1767</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>1721</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>1768</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>1769</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>1770</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>1740</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>1771</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="40.200000000000003" thickBot="1">
+      <c r="A12" s="11">
+        <v>11</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>1772</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>1721</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>1773</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>1738</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>1774</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>1775</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>1776</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="79.8" thickBot="1">
+      <c r="A13" s="11">
+        <v>12</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>1721</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>1778</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>1779</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>1780</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>1781</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>1782</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="40.200000000000003" thickBot="1">
+      <c r="A14" s="11">
+        <v>13</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>1783</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>1721</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>1784</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>1785</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>1786</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>1787</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>1788</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="40.200000000000003" thickBot="1">
+      <c r="A15" s="11">
+        <v>14</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>1789</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>1721</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>1790</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>1738</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>1791</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>1740</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>1792</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>305</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96FF4600-FB83-4A9D-B0AC-C7C4E38930AE}">
+  <dimension ref="A1:J22"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="10.6640625" customWidth="1"/>
+    <col min="2" max="2" width="16.21875" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="5" width="16.44140625" customWidth="1"/>
+    <col min="6" max="6" width="17.109375" customWidth="1"/>
+    <col min="7" max="7" width="18.44140625" customWidth="1"/>
+    <col min="8" max="8" width="23.88671875" customWidth="1"/>
+    <col min="9" max="9" width="11.6640625" customWidth="1"/>
+    <col min="10" max="10" width="13.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="15" thickBot="1">
+      <c r="A1" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="53.4" thickBot="1">
+      <c r="A2" s="11">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>1793</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>1794</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>1795</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>1796</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>1797</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>1798</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="106.2" thickBot="1">
+      <c r="A3" s="11">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>1799</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>1794</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>1800</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>1801</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>1802</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>1803</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>1187</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="79.8" thickBot="1">
+      <c r="A4" s="11">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>1804</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>1794</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>1805</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>1806</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>1807</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>1808</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>1809</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="53.4" thickBot="1">
+      <c r="A5" s="11">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>1810</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>1794</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>1811</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>1812</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>1813</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>1814</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>1815</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="40.200000000000003" thickBot="1">
+      <c r="A6" s="11">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>1816</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>1794</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>662</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>671</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>1817</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="40.200000000000003" thickBot="1">
+      <c r="A7" s="11">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>1818</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>1794</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>666</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>1819</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>324</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>1817</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="53.4" thickBot="1">
+      <c r="A8" s="11">
+        <v>7</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>1820</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>1794</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>668</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>1821</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>1817</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="53.4" thickBot="1">
+      <c r="A9" s="11">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>1822</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>1794</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>670</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>1823</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>334</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>1817</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="53.4" thickBot="1">
+      <c r="A10" s="11">
+        <v>9</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>1824</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>1794</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>1825</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>1826</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>1827</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>1828</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>1829</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="40.200000000000003" thickBot="1">
+      <c r="A11" s="11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>1830</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>1794</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>1831</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>1832</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>1833</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>1834</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>1835</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="53.4" thickBot="1">
+      <c r="A12" s="11">
+        <v>11</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>1794</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>1837</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>1838</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>1839</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>1840</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>1841</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="40.200000000000003" thickBot="1">
+      <c r="A13" s="11">
+        <v>12</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>1842</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>1794</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>1843</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>1844</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>1845</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>1840</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>1846</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="40.200000000000003" thickBot="1">
+      <c r="A14" s="11">
+        <v>13</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>1847</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>1794</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>1848</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>1849</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>1850</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>1840</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>1851</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="53.4" thickBot="1">
+      <c r="A15" s="11">
+        <v>14</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>1852</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>1794</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>1853</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>1854</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>1850</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>1855</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>1856</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="53.4" thickBot="1">
+      <c r="A16" s="11">
+        <v>15</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>1857</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>1794</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>1858</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>1859</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>1860</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>1861</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>1862</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="53.4" thickBot="1">
+      <c r="A17" s="11">
+        <v>16</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>1794</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>1864</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>1865</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>1866</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>1867</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>1868</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="53.4" thickBot="1">
+      <c r="A18" s="11">
+        <v>17</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>1869</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>1794</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>1870</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>1865</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>1871</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>1872</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>1873</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="53.4" thickBot="1">
+      <c r="A19" s="11">
+        <v>18</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>1874</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>1794</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>1875</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>1876</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>1877</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>1861</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>1878</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="66.599999999999994" thickBot="1">
+      <c r="A20" s="11">
+        <v>19</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>1879</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>1794</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>1880</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>1881</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>1882</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>1861</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>1883</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="J20" s="11" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="53.4" thickBot="1">
+      <c r="A21" s="11">
+        <v>20</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>1884</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>1794</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>1885</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>1886</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>1887</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>1888</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>1889</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="53.4" thickBot="1">
+      <c r="A22" s="11">
+        <v>21</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>1890</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>1794</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>1892</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>1893</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>1840</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>1894</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="J22" s="11" t="s">
+        <v>305</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06A6CFA6-4E85-4F91-97F3-FFBEE303B1C4}">
+  <dimension ref="A1:J26"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="14.77734375" customWidth="1"/>
+    <col min="2" max="2" width="15.109375" customWidth="1"/>
+    <col min="3" max="3" width="22.44140625" customWidth="1"/>
+    <col min="4" max="4" width="23.21875" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" customWidth="1"/>
+    <col min="7" max="7" width="16.77734375" customWidth="1"/>
+    <col min="8" max="8" width="16.21875" customWidth="1"/>
+    <col min="9" max="9" width="20.21875" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="28.8">
+      <c r="A1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1895</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="43.2">
+      <c r="A2" s="10" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>1896</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>1897</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="43.2">
+      <c r="A3" s="10" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>1896</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>1898</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="43.2">
+      <c r="A4" s="10" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>1896</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>1899</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="43.2">
+      <c r="A5" s="10" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>1896</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>1900</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="57.6">
+      <c r="A6" s="10" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>1896</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>1901</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="57.6">
+      <c r="A7" s="10" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>1896</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>1902</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="57.6">
+      <c r="A8" s="10" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>1896</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>1903</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="57.6">
+      <c r="A9" s="10" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>1896</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>1904</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="43.2">
+      <c r="A10" s="10" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10" t="s">
+        <v>1905</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="28.8">
+      <c r="A11" s="10" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>1896</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>1906</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="43.2">
+      <c r="A12" s="10" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>1896</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>1907</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="57.6">
+      <c r="A13" s="10" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>1896</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>1908</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="43.2">
+      <c r="A14" s="10" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>1896</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>1909</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="43.2">
+      <c r="A15" s="10" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10" t="s">
+        <v>1910</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="28.8">
+      <c r="A16" s="10" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>1896</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>1911</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="43.2">
+      <c r="A17" s="10" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>1896</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>1912</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="43.2">
+      <c r="A18" s="10" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10" t="s">
+        <v>1896</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>1913</v>
+      </c>
+      <c r="J18" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="43.2">
+      <c r="A19" s="10" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>1896</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>1914</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="43.2">
+      <c r="A20" s="10" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>1896</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>1915</v>
+      </c>
+      <c r="J20" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="43.2">
+      <c r="A21" s="10" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>1896</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>1916</v>
+      </c>
+      <c r="J21" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="57.6">
+      <c r="A22" s="10" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>1896</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>1917</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="57.6">
+      <c r="A23" s="10" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>1716</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>1896</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>1918</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="28.8">
+      <c r="A24" s="10" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>1919</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>1896</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>1920</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="43.2">
+      <c r="A25" s="10" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>1921</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>1922</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="43.2">
+      <c r="A26" s="10" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>1896</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>1923</v>
+      </c>
+      <c r="J26" s="10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M11"/>
